--- a/artfynd/A 60862-2023 artfynd.xlsx
+++ b/artfynd/A 60862-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165832</v>
       </c>
       <c r="B2" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,27 +772,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129166350</v>
+        <v>129166122</v>
       </c>
       <c r="B3" t="n">
-        <v>80174</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679287</v>
+        <v>679281</v>
       </c>
       <c r="R3" t="n">
-        <v>7088718</v>
+        <v>7088582</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,27 +869,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129166122</v>
+        <v>129166350</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>80175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679281</v>
+        <v>679287</v>
       </c>
       <c r="R4" t="n">
-        <v>7088582</v>
+        <v>7088718</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +969,7 @@
         <v>129165679</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129166321</v>
       </c>
       <c r="B6" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60862-2023 artfynd.xlsx
+++ b/artfynd/A 60862-2023 artfynd.xlsx
@@ -772,27 +772,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129166122</v>
+        <v>129166350</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679281</v>
+        <v>679287</v>
       </c>
       <c r="R3" t="n">
-        <v>7088582</v>
+        <v>7088718</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,27 +869,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129166350</v>
+        <v>129166122</v>
       </c>
       <c r="B4" t="n">
-        <v>80175</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679287</v>
+        <v>679281</v>
       </c>
       <c r="R4" t="n">
-        <v>7088718</v>
+        <v>7088582</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 60862-2023 artfynd.xlsx
+++ b/artfynd/A 60862-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165832</v>
       </c>
       <c r="B2" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,27 +772,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129166350</v>
+        <v>129166122</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679287</v>
+        <v>679281</v>
       </c>
       <c r="R3" t="n">
-        <v>7088718</v>
+        <v>7088582</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,27 +869,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129166122</v>
+        <v>129166350</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>80179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679281</v>
+        <v>679287</v>
       </c>
       <c r="R4" t="n">
-        <v>7088582</v>
+        <v>7088718</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +969,7 @@
         <v>129165679</v>
       </c>
       <c r="B5" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129166321</v>
       </c>
       <c r="B6" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60862-2023 artfynd.xlsx
+++ b/artfynd/A 60862-2023 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129165679</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60862-2023 artfynd.xlsx
+++ b/artfynd/A 60862-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165832</v>
       </c>
       <c r="B2" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,27 +772,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129166122</v>
+        <v>129166350</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679281</v>
+        <v>679287</v>
       </c>
       <c r="R3" t="n">
-        <v>7088582</v>
+        <v>7088718</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,27 +869,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129166350</v>
+        <v>129166122</v>
       </c>
       <c r="B4" t="n">
-        <v>80179</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679287</v>
+        <v>679281</v>
       </c>
       <c r="R4" t="n">
-        <v>7088718</v>
+        <v>7088582</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +969,7 @@
         <v>129165679</v>
       </c>
       <c r="B5" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129166321</v>
       </c>
       <c r="B6" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
